--- a/data/trans_orig/P32A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32A-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2007</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427156</t>
+          <t>426788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>438246</t>
+          <t>437591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177702</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>179585</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>606762</t>
+          <t>605395</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>617827</t>
+          <t>617828</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>569727</t>
+          <t>570768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579939</t>
+          <t>579962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>276479</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>278511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>849227</t>
+          <t>849228</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>858503</t>
+          <t>858496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>15412</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317108</t>
+          <t>315625</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328116</t>
+          <t>327692</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125192</t>
+          <t>123395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>445337</t>
+          <t>445289</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>456797</t>
+          <t>457470</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>521824</t>
+          <t>521522</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>527801</t>
+          <t>527805</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>297854</t>
+          <t>298881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>823675</t>
+          <t>823182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>831944</t>
+          <t>831843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34160</t>
+          <t>35166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1849926</t>
+          <t>1850945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1868000</t>
+          <t>1868939</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>885575</t>
+          <t>885511</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>892575</t>
+          <t>892579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2740243</t>
+          <t>2739237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2759218</t>
+          <t>2759126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2012</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2012 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18340</t>
+          <t>19194</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414153</t>
+          <t>413082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423474</t>
+          <t>423202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165603</t>
+          <t>164854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174368</t>
+          <t>174374</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>583100</t>
+          <t>582246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>595561</t>
+          <t>595830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>24177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25127</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>569819</t>
+          <t>568381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>586848</t>
+          <t>587038</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291298</t>
+          <t>291083</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>863891</t>
+          <t>863647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>882496</t>
+          <t>882611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>9452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27424</t>
+          <t>27328</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27304</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>432203</t>
+          <t>432299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>450994</t>
+          <t>450175</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205568</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207746</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640069</t>
+          <t>639838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658199</t>
+          <t>658410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>26046</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31424</t>
+          <t>32062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>530554</t>
+          <t>531104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>546172</t>
+          <t>546807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>352728</t>
+          <t>353553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363920</t>
+          <t>363956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>890571</t>
+          <t>889933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>908054</t>
+          <t>908718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37804</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69413</t>
+          <t>69394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44321</t>
+          <t>45046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79962</t>
+          <t>78254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1965967</t>
+          <t>1965986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1997576</t>
+          <t>1997200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1026850</t>
+          <t>1026322</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1040431</t>
+          <t>1040374</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2999865</t>
+          <t>3001573</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3035506</t>
+          <t>3034781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2016</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415728</t>
+          <t>414780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427316</t>
+          <t>426690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178562</t>
+          <t>177508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>598404</t>
+          <t>598139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>610876</t>
+          <t>610949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27015</t>
+          <t>26683</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30008</t>
+          <t>30812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>547540</t>
+          <t>547872</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>565233</t>
+          <t>564496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>315313</t>
+          <t>314223</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322322</t>
+          <t>322315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>867808</t>
+          <t>867004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>885652</t>
+          <t>885993</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407775</t>
+          <t>406915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>419801</t>
+          <t>419809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>223812</t>
+          <t>224279</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636323</t>
+          <t>635853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649176</t>
+          <t>649128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>15090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26689</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>557039</t>
+          <t>558088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>569363</t>
+          <t>569594</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>388726</t>
+          <t>389538</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>402899</t>
+          <t>402736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>953348</t>
+          <t>952673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>969888</t>
+          <t>969755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27273</t>
+          <t>28847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54016</t>
+          <t>55342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26333</t>
+          <t>24966</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41469</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70542</t>
+          <t>71005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1947346</t>
+          <t>1946020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1974089</t>
+          <t>1972515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1118979</t>
+          <t>1120346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1136729</t>
+          <t>1136498</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3076132</t>
+          <t>3075669</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3105205</t>
+          <t>3105519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le ha molestado que le critiquen su forma de beber en 2023</t>
+          <t>Población según si le ha molestado que le critiquen su forma de beber en 2023 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>12286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>321737</t>
+          <t>322135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>330852</t>
+          <t>330970</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155105</t>
+          <t>155183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>481027</t>
+          <t>480677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>489934</t>
+          <t>490122</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>15333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12152</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461764</t>
+          <t>461423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>472853</t>
+          <t>472662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188803</t>
+          <t>188933</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>198589</t>
+          <t>198547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655405</t>
+          <t>655282</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>669617</t>
+          <t>669195</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>93</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311720</t>
+          <t>311119</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320059</t>
+          <t>319731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>353683</t>
+          <t>352282</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>368441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>670817</t>
+          <t>671732</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>687435</t>
+          <t>687766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18792</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8836</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>21849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>423882</t>
+          <t>424009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>436555</t>
+          <t>437001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282134</t>
+          <t>282195</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>287449</t>
+          <t>287659</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709292</t>
+          <t>709683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>722696</t>
+          <t>722978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38761</t>
+          <t>39309</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29711</t>
+          <t>28537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56615</t>
+          <t>55541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1534776</t>
+          <t>1534228</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1553617</t>
+          <t>1554131</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>993982</t>
+          <t>994306</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1012236</t>
+          <t>1012417</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2535366</t>
+          <t>2536440</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2562270</t>
+          <t>2563444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32A-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426788</t>
+          <t>427565</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>437591</t>
+          <t>438245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>605395</t>
+          <t>606702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>617828</t>
+          <t>617820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>570768</t>
+          <t>570092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579962</t>
+          <t>579984</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>849228</t>
+          <t>849435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>858496</t>
+          <t>858493</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15412</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315625</t>
+          <t>316623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>327692</t>
+          <t>327381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123395</t>
+          <t>125627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>445289</t>
+          <t>446180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>457470</t>
+          <t>457354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>521522</t>
+          <t>521679</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>527805</t>
+          <t>527798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>298881</t>
+          <t>298063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>823182</t>
+          <t>822966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>831843</t>
+          <t>831939</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>29693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35166</t>
+          <t>35509</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1850945</t>
+          <t>1851211</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1868939</t>
+          <t>1868558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>885511</t>
+          <t>885493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>892579</t>
+          <t>892575</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2739237</t>
+          <t>2738894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2759126</t>
+          <t>2759023</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>18946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413082</t>
+          <t>413042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423202</t>
+          <t>423332</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164854</t>
+          <t>165686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174374</t>
+          <t>174376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582246</t>
+          <t>582494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>595830</t>
+          <t>596019</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24177</t>
+          <t>23118</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>24611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>568381</t>
+          <t>569440</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>587038</t>
+          <t>586891</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291083</t>
+          <t>291442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>863647</t>
+          <t>864407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>882611</t>
+          <t>882560</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>432299</t>
+          <t>432519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>450175</t>
+          <t>450818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639838</t>
+          <t>640163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658410</t>
+          <t>658061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26046</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>13058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32062</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>531104</t>
+          <t>530442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>546807</t>
+          <t>546827</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>353553</t>
+          <t>352526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363956</t>
+          <t>363948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>889933</t>
+          <t>891065</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>908718</t>
+          <t>908937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>39128</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69394</t>
+          <t>70569</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>17226</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45046</t>
+          <t>46237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78254</t>
+          <t>80252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1965986</t>
+          <t>1964811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1997200</t>
+          <t>1996252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1026322</t>
+          <t>1027220</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1040374</t>
+          <t>1040624</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3001573</t>
+          <t>2999575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3034781</t>
+          <t>3033590</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>17097</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414780</t>
+          <t>415473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426690</t>
+          <t>427315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177508</t>
+          <t>177498</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>598139</t>
+          <t>598158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>610949</t>
+          <t>610978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26683</t>
+          <t>26323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30812</t>
+          <t>29795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>547872</t>
+          <t>548232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>564496</t>
+          <t>564714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314223</t>
+          <t>314083</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322315</t>
+          <t>322314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>867004</t>
+          <t>868021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>885993</t>
+          <t>885554</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406915</t>
+          <t>407928</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>419809</t>
+          <t>419965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224279</t>
+          <t>223885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>635853</t>
+          <t>636985</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649128</t>
+          <t>649338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>27293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>558088</t>
+          <t>557519</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>569594</t>
+          <t>569488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>389538</t>
+          <t>389722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>402736</t>
+          <t>403035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>952673</t>
+          <t>952744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>969755</t>
+          <t>969947</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>27913</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55342</t>
+          <t>53413</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24966</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>40566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71005</t>
+          <t>71659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1946020</t>
+          <t>1947949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1972515</t>
+          <t>1973449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1120346</t>
+          <t>1120552</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1136498</t>
+          <t>1136949</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3075669</t>
+          <t>3075015</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3105519</t>
+          <t>3106108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>327890</t>
+          <t>348136</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>322135</t>
+          <t>342930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>330970</t>
+          <t>351114</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,27 +6717,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>158790</t>
+          <t>171764</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155183</t>
+          <t>168387</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>486679</t>
+          <t>519900</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>480677</t>
+          <t>514282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>490122</t>
+          <t>523458</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>14245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12022</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,17 +6982,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22429</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>468842</t>
+          <t>492753</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461423</t>
+          <t>486478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>472662</t>
+          <t>497116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>195408</t>
+          <t>216773</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188933</t>
+          <t>208906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>198547</t>
+          <t>220417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,17 +7095,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>664249</t>
+          <t>709527</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655282</t>
+          <t>701056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>669195</t>
+          <t>715399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>200955</t>
+          <t>223195</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200955</t>
+          <t>223195</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>200955</t>
+          <t>223195</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>677711</t>
+          <t>723918</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>677711</t>
+          <t>723918</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>677711</t>
+          <t>723918</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>317157</t>
+          <t>348785</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311119</t>
+          <t>342427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>319731</t>
+          <t>352281</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>364424</t>
+          <t>187363</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>352282</t>
+          <t>177824</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>368441</t>
+          <t>191720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>681582</t>
+          <t>536148</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671732</t>
+          <t>525849</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>687766</t>
+          <t>541709</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>321241</t>
+          <t>354901</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>321241</t>
+          <t>354901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>321241</t>
+          <t>354901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>193588</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>193588</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>368534</t>
+          <t>193588</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>689776</t>
+          <t>548489</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>689776</t>
+          <t>548489</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>689776</t>
+          <t>548489</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21849</t>
+          <t>28051</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>431661</t>
+          <t>453192</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>424009</t>
+          <t>445821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>437001</t>
+          <t>458356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>285725</t>
+          <t>302432</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282195</t>
+          <t>294522</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>287659</t>
+          <t>305598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>717387</t>
+          <t>755625</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709683</t>
+          <t>744315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>722978</t>
+          <t>762316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27988</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>21105</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39309</t>
+          <t>42024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24138</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>49810</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28537</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55541</t>
+          <t>65653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1545549</t>
+          <t>1642867</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1534228</t>
+          <t>1631279</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1554131</t>
+          <t>1652198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1004348</t>
+          <t>878332</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>994306</t>
+          <t>866783</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1012417</t>
+          <t>886020</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2549897</t>
+          <t>2521200</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2536440</t>
+          <t>2505357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2563444</t>
+          <t>2533032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1573537</t>
+          <t>1673303</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1018444</t>
+          <t>897707</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1018444</t>
+          <t>897707</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1018444</t>
+          <t>897707</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2591981</t>
+          <t>2571010</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2591981</t>
+          <t>2571010</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2591981</t>
+          <t>2571010</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
